--- a/f1discussions_samples.xlsx
+++ b/f1discussions_samples.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>open binary prompt, no supporting case made</t>
+          <t>Opinion on Verstappen's race vs quali pace, present analysis</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>proposes format change with reasoning why exciting</t>
+          <t>Proposes 4-driver format with detailed reasoning for it</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>argues George snub narrative wrong, gives reasoning</t>
+          <t>Argues winning team won't celebrate P2, gives reasoning</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>defends proposal with detailed supporting reasoning</t>
+          <t>Supports equal-machinery proposal with extensive reasoning</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>rhetorical question arguing Antonelli not favoured, cites Spain</t>
+          <t>Argues Antonelli isn't favoured, cites Spain example</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>speculates Sainz's future team move</t>
+          <t>Predicts Sainz's future team move from Williams</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>asks readers if jersey is rare</t>
+          <t>Asks if jersey is rare, opinion/experience starter</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>open prompt asking what builds trust</t>
+          <t>Asks what would build trust, opinion discussion starter</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>open-ended discussion prompt about reactions</t>
+          <t>Asks about past reactions to Lewis-Ferrari move</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Aston podium regular by 2027</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -891,10 +891,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -909,7 +905,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>guesses about Red Bull poaching Kimi, future move</t>
+          <t>Speculates about Red Bull poaching Kimi, driver market</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -956,7 +952,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Cadillac chasing US driver future move</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -970,10 +966,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -988,7 +980,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>predicts Austria running order from upgrades</t>
+          <t>Predicts Austria running order, future race performance</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1032,7 +1024,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Hamilton retirement decision for 2027</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1046,10 +1038,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1064,7 +1052,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>proposes idea then asks what do you think</t>
+          <t>Proposes reverse grid idea, opinion discussion starter</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1108,7 +1096,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts first 2025 rookie race winner</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1122,10 +1110,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1140,7 +1124,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>predicts Leclerc could match Hamilton this season</t>
+          <t>Asks to predict Leclerc beating Hamilton this season</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1184,7 +1168,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Ferrari pivoting to 2027 development early</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1198,10 +1182,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1216,7 +1196,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Colapinto return to grid 2027</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1230,10 +1210,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1248,7 +1224,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Verstappen racing WEC after F1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1262,10 +1238,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1280,7 +1252,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>argues Mercedes mishandles George, extensive evidence</t>
+          <t>Argues Mercedes mistreats George, extensive evidence cited</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1337,7 +1309,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts who replaces Alonso at Aston</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1351,10 +1323,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1369,7 +1337,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>defends Piastri citing Qatar weekend details</t>
+          <t>Defends Piastri citing Qatar 2024 dominance</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1421,7 +1389,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>rumor of Verstappen to Mercedes future move</t>
+          <t>Speculates about Verstappen's Red Bull future, Mercedes move</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1460,12 +1428,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>argument</t>
+          <t>speculation</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>argues Lawson rebuilt reputation with reasoning</t>
+          <t>Asks about Lawson's future and top-seat chances</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1519,7 +1487,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Red Bull dropping Tsunoda mid-season</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1533,10 +1501,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1551,7 +1515,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Asks favourite driver of all time, preference starter</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1565,10 +1529,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1583,7 +1543,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>asks about old yellow flag rules, info seeking</t>
+          <t>Asks about past 1999 yellow flag rules</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1627,7 +1587,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Hadjar outscoring Tsunoda this season</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1641,10 +1601,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1659,7 +1615,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Bearman's contract future, Haas or Ferrari</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1673,10 +1629,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1691,7 +1643,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Asks what got you into F1, experience starter</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1705,10 +1657,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1723,7 +1671,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>argues 2027 aero cut is sad, gives reasoning</t>
+          <t>Argues 2027 downforce cut is sad, reasoning given</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1769,7 +1717,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts customer team beating works team 2026</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1783,10 +1731,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1801,7 +1745,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Asks which retired driver to bring back, preference</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1815,10 +1759,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1833,7 +1773,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>predicts whether Tsunoda keeps his seat</t>
+          <t>Predicts Tsunoda swapped before 2027</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1861,7 +1801,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>open prompt asking US fans about popularity</t>
+          <t>Asks about F1 popularity in US, present opinion</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1908,7 +1848,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>open-ended prompt about Button's career</t>
+          <t>Asks opinion on Button's career, present discussion</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1951,7 +1891,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Asks how you cope with off-season, experience starter</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1965,10 +1905,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1983,7 +1919,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Cadillac signing former champion 2027</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1997,10 +1933,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2015,7 +1947,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Bottas return to race seat 2026</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2029,10 +1961,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2047,7 +1975,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Lawson getting another senior Red Bull chance</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2061,10 +1989,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2079,7 +2003,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Audi poaching Mercedes engine staff</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2093,10 +2017,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2111,7 +2031,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Asks earliest F1 memory, experience starter</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2125,10 +2045,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2143,7 +2059,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>open prompt asking US fans about popularity</t>
+          <t>Asks about F1 popularity in US, present opinion</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2184,12 +2100,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>speculation</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>open binary prompt, no case made</t>
+          <t>Asks to predict if Leclerc can win this year</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2232,7 +2148,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>speculates a hypothetical Mercedes lineup</t>
+          <t>Speculates Mercedes running Verstappen and Kimi</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2255,12 +2171,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>speculation</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>open binary prompt, no case made</t>
+          <t>Asks to predict if Leclerc could win this year</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2303,7 +2219,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>hypothetical guess about Alonso vs Norris</t>
+          <t>Predicts hypothetical Alonso vs Norris 2027 matchup</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2346,7 +2262,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>asks reason for Piquet-Hamilton feud</t>
+          <t>Asks reason for Piquet-Hamilton feud, past explanation</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2390,7 +2306,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>predicts Mercedes shifting to favour Antonelli</t>
+          <t>Predicts Antonelli becoming Mercedes number 1</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2418,7 +2334,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>asks if Hamilton has a nickname</t>
+          <t>Asks if Hamilton has a nickname, present info</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2462,7 +2378,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Asks which race made you love F1, experience</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2476,10 +2392,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2494,7 +2406,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>argues Russell fan behavior unfair, cites Toto record</t>
+          <t>Argues Russell fans' behavior unjustified, cites Toto record</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2542,7 +2454,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Asks for your hot take, opinion starter</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2556,10 +2468,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2569,12 +2477,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>speculation</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>open hypothetical discussion prompt</t>
+          <t>Hypothetical: who'd benefit from earlier knockout quali</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2612,12 +2520,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>speculation</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>open hypothetical about combined-team standings</t>
+          <t>Hypothetical standings if all drivers one team</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2660,7 +2568,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>factual history question prompted by rumors</t>
+          <t>Asks if driver ever owned stake, past factual</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2704,7 +2612,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>predicts Bortoleto securing an Audi seat</t>
+          <t>Predicts Bortoleto into Audi works seat 2027</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2732,7 +2640,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>open prompt asking for iconic nicknames</t>
+          <t>Asks for iconic motorsport nicknames, present discussion</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2771,12 +2679,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>speculation</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>open prompt who would you sign</t>
+          <t>Asks who you'd sign in 2027 Lewis-retiring scenario</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2819,7 +2727,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Asks favourite part of race day; opinion/preference starter</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2833,10 +2741,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2851,7 +2755,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>predicts Kimi GOAT, Oscar top 5 careers</t>
+          <t>Predicts who has greater future career; market guess</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2897,7 +2801,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Audi's future debut-year performance</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2911,10 +2815,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2929,7 +2829,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>argues Frank right on Newey, cites AMR26 history</t>
+          <t>Argues Frank was right about Newey with reasoning</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2976,7 +2876,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>open prompt asking reaction, image-based</t>
+          <t>Asks reaction to a past moment; experience starter</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3020,7 +2920,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>open prompt asking reaction, image-based</t>
+          <t>Asks reaction to past moment; experience starter</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3064,7 +2964,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>argues Vettel prime great with stats and quote</t>
+          <t>Argues Vettel's prime greatness with extensive evidence</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3113,7 +3013,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>argues Mercedes favoritism, cites photo/post counts</t>
+          <t>Argues Mercedes favouritism citing post examples</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3162,7 +3062,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts future McLaren collision during title fight</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3176,10 +3076,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3194,7 +3090,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>argues GOATs have slumps, cites many examples</t>
+          <t>Argues GOATs have rough patches with examples</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3242,7 +3138,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>asserts many drivers hit by unreliability point</t>
+          <t>Claims many drivers affected by unreliability, broad point</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3286,7 +3182,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>stat-backed point on Alonso narrow title losses</t>
+          <t>States Alonso lost five close title battles, factual claim</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3329,7 +3225,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Vasseur's future job security at Ferrari</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3343,10 +3239,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3361,7 +3253,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>argues 2014 Hamilton underrated with reliability data</t>
+          <t>Argues 2014 Hamilton underrated with detailed evidence</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3415,7 +3307,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>claims races better without mandatory one-stop</t>
+          <t>Claims races better without mandatory one-stop</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3458,7 +3350,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>argues over-35 drivers underappreciated, cites declines</t>
+          <t>Argues over-35 drivers underappreciated with reasoning</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3505,7 +3397,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Guesses Sainz privately regrets leaving Ferrari</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3519,10 +3411,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3537,7 +3425,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>wants refueling back, gives safety/strategy reasoning</t>
+          <t>Argues for refueling return with reasoning</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3581,7 +3469,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>speculates which Ferrari driver gets car priority</t>
+          <t>Predicts which driver Ferrari builds 2027 car around</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3609,7 +3497,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>predicts Austria over/underperformers from circuit history</t>
+          <t>Asks who underperforms at upcoming Austria race</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3658,7 +3546,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts whether 2026 regs close grid</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3672,10 +3560,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3685,12 +3569,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>argument</t>
+          <t>question</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>observation backed by examples across Hamilton wins</t>
+          <t>Shares trivia observation; light discussion starter</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -3736,7 +3620,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>predicts Hadjar promoted to senior Red Bull seat</t>
+          <t>Predicts Hadjar promotion to senior Red Bull seat</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3764,7 +3648,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Claims Ferrari built best car, cites working upgrades/strategy</t>
+          <t>Asserts Ferrari built best car, upgrades working</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -3807,7 +3691,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Leclerc's future title-winning car timing</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3821,10 +3705,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3839,7 +3719,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Title-only claim Piastri underrated; asserts a position</t>
+          <t>Claims Piastri is underrated talent</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -3882,7 +3762,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Speculates Antonelli future move to Ferrari</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3896,10 +3776,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3914,7 +3790,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Hot take comparing F1 fandom to Dream SMP, with reasoning</t>
+          <t>Argues F1 becoming Dream SMP with reasoning</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -3958,7 +3834,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Asserts Merc favoring George via social media as evidence</t>
+          <t>Claims Merc doing damage control, cites posts</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4001,7 +3877,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Rumor about unconfirmed Mercedes 2027 offer to Verstappen</t>
+          <t>Rumor about Max's possible Mercedes 2027 offer</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4044,7 +3920,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>predicts Aston-Honda becoming title contenders</t>
+          <t>Predicts Honda/Aston title contention by 2028</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4072,7 +3948,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Detailed technical analysis of four teams with evidence</t>
+          <t>Detailed analysis of top teams with evidence</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -4135,7 +4011,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Argues drivers equal, cites same brakes/setup as evidence</t>
+          <t>Argues both drivers comfortable citing setup details</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -4178,7 +4054,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Argues Leclerc underperforming, cites crashes despite question framing</t>
+          <t>Argues Leclerc underperforming with crash evidence</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -4229,7 +4105,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Guesses unconfirmed info about drivers sharing data benefit</t>
+          <t>Asks confirmation of non-obvious data-sharing benefit</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -4272,7 +4148,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Asks which rule fans wish returned; preference starter</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -4286,10 +4162,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4304,7 +4176,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Argues fans overanalyze, defends Merc with reasoning</t>
+          <t>Argues fans overanalyse, defends Mercedes with reasoning</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4351,7 +4223,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Argues George/Merc dynamic with sources and reasoning</t>
+          <t>Argues about George/Mercedes situation with reasoning</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -4402,7 +4274,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Open-ended prompt comparing current to past drivers</t>
+          <t>Asks which current drivers resemble past ones</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -4446,7 +4318,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Open-ended hypothetical about motorsport World Cup lineups</t>
+          <t>Asks which countries best motorsport lineup; opinion starter</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -4490,7 +4362,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Argues Merc operational errors cost wins, race-by-race evidence</t>
+          <t>Argues Hamilton lost wins via team errors, evidence</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -4552,7 +4424,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Argues multi-stop races better despite question framing</t>
+          <t>Argues races better without forced one-stop</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -4596,7 +4468,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Argues Vettel resonated uniquely, gives reasoning</t>
+          <t>Argues Vettel resonated uniquely with fans, reasoning</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -4642,7 +4514,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Asks most underrated circuit; preference starter</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -4656,10 +4528,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4674,7 +4542,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Open-ended prompt asking opinions on Mercedes</t>
+          <t>Asks general opinion on Mercedes; open discussion</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4718,7 +4586,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Predicts whether Alonso will retire this season</t>
+          <t>Predicts whether Alonso retires this season</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -4761,7 +4629,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Open-ended prompt on Mercedes treating Russell unfairly</t>
+          <t>Asks opinion whether Mercedes mean to Russell</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -4804,7 +4672,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Argues multi-stop races more enjoyable, gives reasoning</t>
+          <t>Argues multi-stop races more enjoyable with reasoning</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -4843,12 +4711,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>argument</t>
+          <t>question</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Argues Lando over Max, cites impressive form, despite question</t>
+          <t>Asks opinion whether Max still best this year</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4892,7 +4760,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Asks favourite team radio moment; preference starter</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -4906,10 +4774,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4924,7 +4788,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Predicts Oscar leaving McLaren via Webber leverage</t>
+          <t>Predicts Oscar eventually leaving McLaren, market guess</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -4970,7 +4834,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Argues Vettel's early success caused hate, with reasoning</t>
+          <t>Argues Vettel victim of early success with reasoning</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -5018,7 +4882,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Analyzes Stroll's 2023 decline with race-by-race evidence</t>
+          <t>Argues about Stroll's 2023 slump with evidence</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -5073,7 +4937,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Argues Antonelli should've been penalized, cites track limits</t>
+          <t>Argues Antonelli deserved penalty citing track limits</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -5116,7 +4980,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Open-ended prompt on best driver-in-wall moments</t>
+          <t>Asks best driver-in-wall moment; preference starter</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -5160,7 +5024,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Title-only claim F1 sleeping on Gasly, asserts position</t>
+          <t>Claims fans sleeping on Gasly</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -5203,7 +5067,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Gasly's future shot at top team</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -5217,10 +5081,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5235,7 +5095,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Predicts Lawson guaranteed 2027 seat, unconfirmed</t>
+          <t>Predicts Lawson secured 2027 seat</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -5273,12 +5133,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>speculation</t>
+          <t>question</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Guesses hypothetical 12th team, predicts Lotus</t>
+          <t>Asks who hypothetical 12th team would be</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -5322,7 +5182,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Predicts who replaces Verstappen if he leaves</t>
+          <t>Predicts who replaces Max if he leaves</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -5365,7 +5225,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Audi-rebrand will still struggle next season</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -5379,10 +5239,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5397,7 +5253,7 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts future poaching of McLaren technical staff</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -5411,10 +5267,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5429,7 +5281,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Argues Merc favoritism clear, cites YouTube post evidence</t>
+          <t>Claims favoritism, cites Mercedes video as evidence</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -5467,12 +5319,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>argument</t>
+          <t>question</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Argues driving-style suits some drivers, gives reasoning</t>
+          <t>Asks explanation of current driving-style differences</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -5516,7 +5368,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Open-ended question about how wing got damaged</t>
+          <t>Asks about past wing damage with image</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -5561,7 +5413,7 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Norris's future mental recovery and career</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -5575,10 +5427,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5593,7 +5441,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Argues Toto is Merc's problem, with reasoning</t>
+          <t>Argues Toto is Merc's problem with reasoning</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -5641,7 +5489,7 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Favourite team principal personality discussion starter</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -5655,10 +5503,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5673,7 +5517,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Rosberg's reasoned position on team orders for Russell</t>
+          <t>States Rosberg's position on team-orders decision</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -5716,7 +5560,7 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Argues VCARB/Alpine battle great, cites drivers/engine</t>
+          <t>Opinionated midfield-battle take backed by reasoning</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -5760,7 +5604,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Open-ended prompt comparing F1 to sports types</t>
+          <t>Opinion discussion comparing F1 to sports cultures</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -5803,7 +5647,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Open-ended prompt asking for slowest-prime-race suggestions</t>
+          <t>Discussion of past slowest prime races</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -5863,7 +5707,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>How to explain F1 to newcomers</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -5877,10 +5721,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5895,7 +5735,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Argues George underrated using pit error/pace evidence</t>
+          <t>Argues George underrated using race-by-race reasoning</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -5945,7 +5785,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Argues Merc disrespecting George, cites podium snub evidence</t>
+          <t>Argues Merc disrespects George with evidence</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -5991,7 +5831,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts future Antonelli contract extension</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -6005,10 +5845,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6023,7 +5859,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Detailed driver assessments backed by reasoning</t>
+          <t>Detailed argument assessing multiple drivers' ceilings</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -6071,7 +5907,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Stat-based claim ranking drivers by avg finish</t>
+          <t>Presents finishing-position stats as a claim</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -6117,7 +5953,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Driver-market guess about Russell's future move</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -6131,10 +5967,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6149,7 +5981,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Open-ended: strategy vs wheel-to-wheel preference</t>
+          <t>Preference: strategy versus wheel-to-wheel racing</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -6193,7 +6025,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Open-ended prompt about fan behavior/TeamLH</t>
+          <t>Asks opinions on present fan-behavior dynamics</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -6238,7 +6070,7 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Stroll leaving F1 by 2027</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -6252,10 +6084,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6317,7 +6145,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Speculates future Verstappen-Hamilton team pairing</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -6331,10 +6159,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6349,7 +6173,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Compares Norris to Hamilton 2009 with evidence</t>
+          <t>Argues Norris parallels Hamilton 2009 with reasoning</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -6394,7 +6218,7 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Argues Hamilton's position skewed by rivals' DNFs</t>
+          <t>Argues against points narratives citing rivals' DNFs</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -6440,7 +6264,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Argues Norris ahead despite DNFs, with reasoning</t>
+          <t>Argues points misleading given Norris's DNFs</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -6486,7 +6310,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Binary question, then supports engineer being sloppy</t>
+          <t>Binary question then supports engineer being sloppy</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -6531,7 +6355,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Predicts Verstappen's future like Hamilton's era</t>
+          <t>Predicts Verstappen's future under new regs</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -6575,7 +6399,7 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Which circuit you'd want returning to calendar</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -6589,10 +6413,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6607,7 +6427,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Argues he can root for any driver, with reasoning</t>
+          <t>Argues for supporting any driver, with reasoning</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -6654,7 +6474,7 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Argues Leclerc has no luck, backed by examples</t>
+          <t>Argues Leclerc unluckiest, citing missed gifted wins</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
@@ -6701,7 +6521,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>predicts Hamilton's eventual Ferrari replacement</t>
+          <t>Driver-market guess on Hamilton's Ferrari replacement</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -6729,7 +6549,7 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Proposes carry-over rewards with reasoning</t>
+          <t>Proposes carry-over rewards idea with reasoning</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -6776,7 +6596,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts whether Russell wins a championship</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -6790,10 +6610,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6808,7 +6624,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Asks for predictions on rookies' future careers</t>
+          <t>Asks predictions on rookies' future careers</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -6856,7 +6672,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Which current rivalry most compelling to you</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -6870,10 +6686,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6888,7 +6700,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Argues sub punishes opinions, backed by reasoning</t>
+          <t>Argues sub punishes nuanced opinions with reasoning</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -6937,7 +6749,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts next Red Bull car undriveable without Max</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -6951,10 +6763,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6969,7 +6777,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Open-ended prompt about hardest Wordle category</t>
+          <t>Brainstorming hardest F1 Wordle categories</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -7023,7 +6831,7 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Open-ended: does Stroll deserve the hate</t>
+          <t>Opinion: does Stroll deserve the hate</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -7066,7 +6874,7 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Most heartbreaking race you've watched</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
@@ -7080,10 +6888,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7098,7 +6902,7 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Open-ended: how happy about first Ferrari win</t>
+          <t>Asks feelings about past Ferrari win</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -7141,7 +6945,7 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Asks for advice/experience on Thursday at GP</t>
+          <t>Asks for experiences/advice on Thursday at Silverstone</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -7190,7 +6994,7 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Driver-market guess on Perez joining Cadillac</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -7204,10 +7008,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
-      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7222,7 +7022,7 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Open-ended: why is Red Bull so slow</t>
+          <t>Asks explanation of Red Bull's current slowness</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -7265,7 +7065,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Predicts Tsolov to F1 if Lawson fails</t>
+          <t>Predicts F2 drivers' future F1 moves</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -7309,7 +7109,7 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Mercedes winning before Ferrari this year</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -7323,10 +7123,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
-      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7341,7 +7137,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Predicts Tsolov to Aston, future driver moves</t>
+          <t>Predicts F2 drivers' future team destinations</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -7385,7 +7181,7 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Best era of F1 you've personally watched</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
@@ -7399,10 +7195,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
-      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7412,12 +7204,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>speculation</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Quotes Toto, asks if Lewis can win WDC</t>
+          <t>Asks whether Lewis can still win title</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -7465,12 +7257,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>speculation</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Open-ended about Williams' future and Sainz</t>
+          <t>Asks Williams's future and Sainz's seat</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -7518,7 +7310,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Open-ended: most dramatic reputation shift?</t>
+          <t>Discussion of Leclerc's present reputation shift</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -7562,7 +7354,7 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Piastri becoming McLaren's number one</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -7576,10 +7368,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7594,7 +7382,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Argues Russell will get team orders, with reasoning</t>
+          <t>Argues Russell faces team orders with reasoning</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -7638,7 +7426,7 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Argues Sainz overrated, extensive supporting reasoning</t>
+          <t>Argues Sainz overrated with extensive reasoning</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -7681,12 +7469,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>speculation</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Binary but open discussion on SF-26 contender</t>
+          <t>Asks if SF-26 is future title contender</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -7730,7 +7518,7 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Ferrari making more baffling strategy calls</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
@@ -7744,10 +7532,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7762,7 +7546,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Favourite F1 documentary or book recommendation</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -7776,10 +7560,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7794,7 +7574,7 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Driver-market guess on Norris to Red Bull</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -7808,10 +7588,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7826,7 +7602,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts future regret over Honda/Red Bull engine outcome</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -7840,10 +7616,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7858,7 +7630,7 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts next driver to reach 100 wins</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -7872,10 +7644,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7890,7 +7658,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Speculates George move to Audi, future</t>
+          <t>Driver-market guess about George moving to Audi</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -7929,12 +7697,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>speculation</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>New fan asks if George will be fired</t>
+          <t>Asks about future firing and possible destination</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -7978,7 +7746,7 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Guesses about Max's future contract and staying</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -7992,10 +7760,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8010,7 +7774,7 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>Open-ended hypothetical about Toto at McLaren</t>
+          <t>Hypothetical opinion starter about Toto handling past season</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -8053,7 +7817,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Argues Russell mistreated, backed by examples</t>
+          <t>Argues Mercedes mistreats Russell, backed with examples</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -8099,7 +7863,7 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>Asks how Ascari won 5 grand slams</t>
+          <t>Asks how Ascari achieved past wins; historical discussion</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
@@ -8143,7 +7907,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Argues DRS zone placement, detailed reasoning</t>
+          <t>Argues DRS zone placement is wrong with reasoning</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -8190,7 +7954,7 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>New fan asks why Kimi penalty not reviewed</t>
+          <t>Asks why stewards didn't review Kimi's track limits</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
@@ -8234,7 +7998,7 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Open-ended: feelings on current regulations</t>
+          <t>Asks opinions on current regulations and racing</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -8294,7 +8058,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Hamilton's future title chances with Ferrari</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -8308,10 +8072,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8326,7 +8086,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts surprise package for second half season</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -8340,10 +8100,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8358,7 +8114,7 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>Argues cars look more natural, with evidence</t>
+          <t>Argues cars look more natural, backed by Barcelona observations</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -8402,7 +8158,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>predicts Verstappen forcing an early Red Bull exit</t>
+          <t>Predicts Verstappen could leave Red Bull mid-contract</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -8430,7 +8186,7 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Open preference starter about track to attend</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -8444,10 +8200,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr"/>
-      <c r="H197" t="inlineStr"/>
-      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8462,7 +8214,7 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Detailed tyre/downforce theory backed by reasoning</t>
+          <t>Argues championship decided on tyres with detailed reasoning</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -8521,7 +8273,7 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Asks if customer teams get upgraded engine</t>
+          <t>Asks factual rules about customer teams getting engine</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
@@ -8565,7 +8317,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Tsunoda's future move to IndyCar/WEC</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -8579,10 +8331,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8597,7 +8345,7 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>predicts Norris possibly leaving McLaren</t>
+          <t>Predicts Norris's future move if Piastri beats him</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
@@ -8625,7 +8373,7 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts future grid expansion to 12 teams</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -8639,10 +8387,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8657,7 +8401,7 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Argues Hamilton VSC-lucky, backed by comparison</t>
+          <t>Argues Hamilton got lucky via VSC with evidence</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -8709,7 +8453,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Argues Oscar below Lando, with reasoning</t>
+          <t>Argues Oscar not at Lando's level with reasoning</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -8753,7 +8497,7 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Asks for predictions on rest of season</t>
+          <t>Asks for predictions about rest of season</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -8797,7 +8541,7 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Argues races improving, backed by examples</t>
+          <t>Argues races better than last season with examples</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -8849,7 +8593,7 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Mercedes engine dominance in 2026 reset</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
@@ -8863,10 +8607,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr"/>
-      <c r="H207" t="inlineStr"/>
-      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -8881,7 +8621,7 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Asks about viewers' watching habits and experiences</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -8895,10 +8635,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8908,12 +8644,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>argument</t>
+          <t>question</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Binary hypothetical, supports Lewis still wins</t>
+          <t>Hypothetical about how past race result changes</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -8959,7 +8695,7 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Argues Barcelona most entertaining, with evidence</t>
+          <t>Argues Barcelona most entertaining, backed with reasons</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -8999,12 +8735,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>speculation</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Asks where McLaren finishes, open discussion</t>
+          <t>Asks where teams/drivers finish; predicting future standings</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
@@ -9052,7 +8788,7 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Quotes Windsor comparing driving styles, reasoning</t>
+          <t>Argues driving-style comparison, attributing traits with reasoning</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -9097,7 +8833,7 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Speculates Bearman's future career path</t>
+          <t>Guesses about Bearman's future career path</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
@@ -9141,7 +8877,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Reports confirmed wing error, factual evidence</t>
+          <t>States Merc confirmed balance issue with quoted evidence</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -9185,7 +8921,7 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Claims races better when not one-stop</t>
+          <t>Argues non-one-stop races are much better</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
@@ -9228,7 +8964,7 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Asks community why they joined the subreddit</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -9242,10 +8978,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -9260,7 +8992,7 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Speculates Mercedes will favour Antonelli</t>
+          <t>Predicts whether Mercedes will favour Antonelli future</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
@@ -9310,7 +9042,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Asks if Lewis's first win expected this early</t>
+          <t>Asks if people expected Hamilton's first win; past expectations</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -9354,7 +9086,7 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>predicts Red Bull's engine underperforming</t>
+          <t>Predicts Red Bull engine flop in 2026</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
@@ -9382,7 +9114,7 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Open-ended hypothetical about race rules</t>
+          <t>Hypothetical rules question about 21 retirements</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -9425,7 +9157,7 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>asks for predictions of the future 2027 grid</t>
+          <t>Predicts the 2027 grid after reg reset</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
@@ -9453,7 +9185,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Asks readers to compare team principals</t>
+          <t>Asks opinion comparing how bosses treat drivers</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -9496,7 +9228,7 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Praises commentator backed with specific examples</t>
+          <t>Argues Jacques is best commentator with examples</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
@@ -9545,7 +9277,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Argues Leclerc renewal was wrong with stats</t>
+          <t>Argues Leclerc renewal was mistake with reasoning</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -9594,7 +9326,7 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>States Sainz was better choice, opinion stated</t>
+          <t>Asks opinion but argues Sainz was better choice</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
@@ -9637,7 +9369,7 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>predicts Cadillac signing a top driver</t>
+          <t>Predicts Cadillac poaching big name year two</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -9665,7 +9397,7 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Argues Lando best-of-rest with data over seasons</t>
+          <t>Argues Lando is best of rest with evidence</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
@@ -9717,7 +9449,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Guesses about Russell winning future title</t>
+          <t>Asks whether Russell can win future championship</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -9762,7 +9494,7 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Asks readers to rank two drivers</t>
+          <t>Asks how to rank drivers this season; opinion starter</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
@@ -9806,7 +9538,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Asks for technical F1 sources</t>
+          <t>Asks for technical F1 sources; preference/resource discussion</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -9851,7 +9583,7 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Argues Norris overhyped, compares to Vettel</t>
+          <t>Argues Norris overhyped with comparison reasoning</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
@@ -9897,7 +9629,7 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Verstappen ending up at Aston eventually</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
@@ -9911,10 +9643,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr"/>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr"/>
-      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -9929,7 +9657,7 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Asks opinion on which driver becomes legend</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
@@ -9943,10 +9671,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr"/>
-      <c r="G233" t="inlineStr"/>
-      <c r="H233" t="inlineStr"/>
-      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -9961,7 +9685,7 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Guesses Leclerc could leave Ferrari in future</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -9975,10 +9699,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr"/>
-      <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr"/>
-      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -9993,7 +9713,7 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Asks which young driver people are excited about</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
@@ -10007,10 +9727,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr"/>
-      <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr"/>
-      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -10025,7 +9741,7 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Asks which Stroll podium most deserved</t>
+          <t>Asks opinion ranking past Stroll podiums</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -10068,7 +9784,7 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Hypothetical pick-two-drivers prompt</t>
+          <t>Hypothetical opinion starter about signing past drivers</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
@@ -10111,7 +9827,7 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Argues Max thrived vs Hamilton with examples</t>
+          <t>Argues only Max thrived against Hamilton with examples</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -10160,7 +9876,7 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Predicts Russell leaving Mercedes, guesses destination</t>
+          <t>Guesses which team George transfers to</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
@@ -10206,7 +9922,7 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Predicts future non-Merc winners</t>
+          <t>Predicts which non-Merc driver wins next</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -10250,7 +9966,7 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Defends Piastri citing recency bias, examples</t>
+          <t>Argues Oscar criticism is recency bias with reasoning</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
@@ -10296,7 +10012,7 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Asks which moment felt more personal</t>
+          <t>Asks which past event felt more personal; opinion starter</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -10344,7 +10060,7 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Argues Norris beats Piastri with stats</t>
+          <t>Claims Norris superior, backs with 19-3 data pattern</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
@@ -10406,7 +10122,7 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Argues young drivers favored by reg change</t>
+          <t>Reasoned case for generational driver divide</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -10455,7 +10171,7 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Asks what would make title fight interesting</t>
+          <t>Open discussion on making title fight interesting</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
@@ -10499,7 +10215,7 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Question framing but argues Leclerc crashes, stats</t>
+          <t>Argues Leclerc error-prone, cites retirement-rate stats</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -10543,7 +10259,7 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Favourite livery, pure aesthetics opinion starter</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
@@ -10557,10 +10273,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F247" t="inlineStr"/>
-      <c r="G247" t="inlineStr"/>
-      <c r="H247" t="inlineStr"/>
-      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -10570,12 +10282,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>speculation</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Binary trivia question, no supporting argument</t>
+          <t>Asks about non-obvious record/stat first-time fact</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -10618,7 +10330,7 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Question framing but argues Merc underperformed, evidence</t>
+          <t>Argues Merc underperformed, extensive supporting detail</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
@@ -10665,7 +10377,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Asks for best F1 driver song</t>
+          <t>Favourite F1 driver song, preference starter</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -10709,7 +10421,7 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Wonders how quickly Leclerc adapts, future guess</t>
+          <t>Guesses how quickly Charles adapts, future/non-obvious</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
@@ -10753,7 +10465,7 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Argues Russell snubbed by team, observation</t>
+          <t>Points out team absence, sympathy backed by observation</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -10797,7 +10509,7 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Speculates Rosberg has regrets, unknowable feelings</t>
+          <t>Guesses Rosberg's private regrets, non-obvious info</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
@@ -10847,7 +10559,7 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Emotional experience of driver's first win</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -10861,10 +10573,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr"/>
-      <c r="G254" t="inlineStr"/>
-      <c r="H254" t="inlineStr"/>
-      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -10879,7 +10587,7 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Asks if driver makes all-time top 10</t>
+          <t>Opinion on retirement and all-time ranking starter</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
@@ -10922,7 +10630,7 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Argues Piastri hate unfair, cites H2H stats</t>
+          <t>Argues Piastri hate unfair, cites quali H2H</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -10970,7 +10678,7 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts Jos comment hinting Max's future move</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
@@ -10984,10 +10692,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr"/>
-      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -11002,7 +10706,7 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Predicts Mercedes Austria performance with history</t>
+          <t>Predicts Mercedes Austria performance, future prediction</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -11046,7 +10750,7 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>speculates a future Alonso team switch</t>
+          <t>Predicts Alonso making future team switch</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
@@ -11074,7 +10778,7 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Question framing but argues Max performing well</t>
+          <t>Argues Max not underperforming, reasons field spread</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -11120,7 +10824,7 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Driver vs car debate, open opinion</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
@@ -11134,10 +10838,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="inlineStr"/>
-      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -11152,7 +10852,7 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Bare open-ended question, no body</t>
+          <t>Opinion on Max's present-season performance, starter</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -11190,12 +10890,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>speculation</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Asks if Charles beats Max equal cars</t>
+          <t>Hypothetical equal-car outcome, guesses non-obvious</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
@@ -11238,7 +10938,7 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>New fan asking how contracts work</t>
+          <t>New fan asks how driver contracts work</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -11282,7 +10982,7 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Which driver to have coffee with, personality</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
@@ -11296,10 +10996,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr"/>
-      <c r="H265" t="inlineStr"/>
-      <c r="I265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -11314,7 +11010,7 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>synthetic speculation</t>
+          <t>Predicts McLaren constructors three years running</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
@@ -11328,10 +11024,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr"/>
-      <c r="H266" t="inlineStr"/>
-      <c r="I266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -11346,7 +11038,7 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Argues Russell race pace weak, long evidence</t>
+          <t>Argues Russell race pace point, detailed history</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
@@ -11390,7 +11082,7 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Asks best driver of 2026</t>
+          <t>Opinion on best driver 2026, starter</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
@@ -11433,7 +11125,7 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Argues Merc ruined Russell race, detailed reasoning</t>
+          <t>Argues Merc not Russell ruined race, reasoning</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
@@ -11482,7 +11174,7 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Argues Russell underperforming with reasoning</t>
+          <t>Argues Russell underperforming, backed by season analysis</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
@@ -11528,7 +11220,7 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Argues pattern via stats, tongue-in-cheek conclusion</t>
+          <t>Argues a pattern with cited coincidences</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
@@ -11567,12 +11259,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>argument</t>
+          <t>speculation</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Question framing but argues George decline, examples</t>
+          <t>Asks non-obvious cause of George's slowness</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -11616,7 +11308,7 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Asks who is top in spec series</t>
+          <t>Hypothetical spec-series ranking opinion starter</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
@@ -11662,7 +11354,7 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Argues several points proven wrong, evidence</t>
+          <t>Multiple reasoned claims about season's surprises</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -11712,7 +11404,7 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Race-weekend ritual, experience sharing</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
@@ -11726,10 +11418,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F275" t="inlineStr"/>
-      <c r="G275" t="inlineStr"/>
-      <c r="H275" t="inlineStr"/>
-      <c r="I275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -11739,12 +11427,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>speculation</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Asks why Russell faster than Kimi stints</t>
+          <t>Asks non-obvious cause of pace swing</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -11787,7 +11475,7 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Question framing but argues Lewis building team, evidence</t>
+          <t>Argues Lewis building team, cites Charles comments</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
@@ -11835,7 +11523,7 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>synthetic question</t>
+          <t>Best overtake seen live, experience</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
@@ -11849,10 +11537,6 @@
           <t>synthetic</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr"/>
-      <c r="G278" t="inlineStr"/>
-      <c r="H278" t="inlineStr"/>
-      <c r="I278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -11867,7 +11551,7 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Asks others about losing confidence in driver</t>
+          <t>Shares experience of losing driver confidence</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
@@ -11915,7 +11599,7 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Question framing but argues Piastri grip struggles</t>
+          <t>Argues low grip hurts Piastri, reasoned theory</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
@@ -11959,7 +11643,7 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Claims Norris peak form, opinion stated</t>
+          <t>Claims Norris at career-best level, asserted point</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
@@ -12002,7 +11686,7 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Argues Lewis built good Ferrari team, examples</t>
+          <t>Argues Lewis building team, cites engineers/changes</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
@@ -12047,7 +11731,7 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Predicts Hamilton title fight via ADUO gains</t>
+          <t>Predicts Hamilton title contention via ADUO gains</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
